--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/5ae0b/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/f0de2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FE1A8C5-4B39-2943-A7F5-652FDD41BD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{056DAA92-D8BD-1B4D-8041-79539E0BF11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11940" yWindow="5940" windowWidth="27700" windowHeight="16860" xr2:uid="{F83CD4D7-03C6-D841-9693-CDD177916ED2}"/>
+    <workbookView xWindow="-26200" yWindow="9200" windowWidth="27700" windowHeight="16860" xr2:uid="{A3C77F66-9BE8-F84F-9382-2D1C6E93537B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
   <si>
     <t>Folder Name</t>
   </si>
@@ -131,7 +131,7 @@
     <t>C2</t>
   </si>
   <si>
-    <t>CM</t>
+    <t>C3</t>
   </si>
   <si>
     <t>IB</t>
@@ -320,28 +320,25 @@
     <t>nf_M1</t>
   </si>
   <si>
-    <t>tmp_20241105061044644042572_tt</t>
+    <t>tmp_20241106043301135015506_tt</t>
   </si>
   <si>
     <t>tt</t>
   </si>
   <si>
-    <t>32.75p</t>
-  </si>
-  <si>
-    <t>0.25p</t>
-  </si>
-  <si>
-    <t>21.5p</t>
-  </si>
-  <si>
-    <t>1.25u</t>
-  </si>
-  <si>
-    <t>100.0k</t>
-  </si>
-  <si>
-    <t>4.75u</t>
+    <t>7.6p</t>
+  </si>
+  <si>
+    <t>0.1p</t>
+  </si>
+  <si>
+    <t>9.7p</t>
+  </si>
+  <si>
+    <t>1.75u</t>
+  </si>
+  <si>
+    <t>400.0k</t>
   </si>
   <si>
     <t>0.25u</t>
@@ -350,64 +347,46 @@
     <t>1</t>
   </si>
   <si>
+    <t>9.5u</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10.0u</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>6.75u</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>15.0u</t>
+  </si>
+  <si>
+    <t>60.0n</t>
+  </si>
+  <si>
+    <t>7.5u</t>
+  </si>
+  <si>
+    <t>4.25u</t>
+  </si>
+  <si>
     <t>8.75u</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>5.25u</t>
-  </si>
-  <si>
-    <t>2.75u</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10.0u</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1.75u</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>15.0u</t>
-  </si>
-  <si>
-    <t>60.0n</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>9.25u</t>
-  </si>
-  <si>
-    <t>5.75u</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>9.5u</t>
-  </si>
-  <si>
-    <t>5.5u</t>
-  </si>
-  <si>
-    <t>3.0u</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>8.0u</t>
+    <t>9.75u</t>
   </si>
 </sst>
 </file>
@@ -816,7 +795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4F7917-DFC2-9D40-BF9D-62D20E3E2D00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC731451-4C3A-7B44-8EFD-D9D7F44CF749}">
   <dimension ref="A1:CP2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
@@ -1112,85 +1091,85 @@
         <v>95</v>
       </c>
       <c r="C2" s="2">
-        <v>-6.2534155317463702E-2</v>
+        <v>-6.3988800238670193E-2</v>
       </c>
       <c r="D2" s="2">
-        <v>7.7520699999999995E-6</v>
+        <v>7.4068099999999998E-6</v>
       </c>
       <c r="E2" s="2">
-        <v>3.628888888888879E-3</v>
+        <v>1.953333333333251E-3</v>
       </c>
       <c r="F2" s="2">
-        <v>4.2088888888890284E-3</v>
+        <v>1.5911111111110989E-3</v>
       </c>
       <c r="G2" s="2">
-        <v>0.80174999999999996</v>
+        <v>1.660700000000001</v>
       </c>
       <c r="H2" s="2">
-        <v>48.51557770748186</v>
+        <v>53.434802469729092</v>
       </c>
       <c r="I2" s="2">
-        <v>45.345756210900689</v>
+        <v>50.089611247586333</v>
       </c>
       <c r="J2" s="2">
-        <v>29.013162344728251</v>
+        <v>33.651478980556831</v>
       </c>
       <c r="K2" s="2">
-        <v>9.824417618078062</v>
+        <v>14.951439551350621</v>
       </c>
       <c r="L2" s="2">
-        <v>4.0959955542426121</v>
+        <v>4.001817903512884</v>
       </c>
       <c r="M2" s="2">
-        <v>48.048936592703228</v>
+        <v>55.355915407251601</v>
       </c>
       <c r="N2" s="2">
-        <v>45.181816995471422</v>
+        <v>50.967479251408257</v>
       </c>
       <c r="O2" s="2">
-        <v>29.13739095143362</v>
+        <v>33.805437219526993</v>
       </c>
       <c r="P2" s="2">
-        <v>9.9580772587214579</v>
+        <v>15.040982564138529</v>
       </c>
       <c r="Q2" s="2">
-        <v>4.5010945781254383</v>
+        <v>4.4498203777529746</v>
       </c>
       <c r="R2" s="2">
-        <v>94.062510000000003</v>
+        <v>97.535510000000002</v>
       </c>
       <c r="S2" s="2">
-        <v>125608.7</v>
+        <v>235298.5</v>
       </c>
       <c r="T2" s="2">
-        <v>96.745149999999995</v>
+        <v>106.86020000000001</v>
       </c>
       <c r="U2" s="2">
-        <v>130491</v>
+        <v>200315.1</v>
       </c>
       <c r="V2" s="2">
-        <v>96.034809999999993</v>
+        <v>99.991349999999997</v>
       </c>
       <c r="W2" s="2">
-        <v>82579.740000000005</v>
+        <v>171402.4</v>
       </c>
       <c r="X2" s="2">
-        <v>98.041420000000002</v>
+        <v>108.1123</v>
       </c>
       <c r="Y2" s="2">
-        <v>130665.1</v>
+        <v>202191.2</v>
       </c>
       <c r="Z2" s="2">
-        <v>9.3623000000000012E-2</v>
+        <v>8.8400999999999952E-2</v>
       </c>
       <c r="AA2" s="2">
-        <v>7.0465000000000055E-2</v>
+        <v>6.920599999999999E-2</v>
       </c>
       <c r="AB2" s="2">
-        <v>7.1819000000000077E-2</v>
+        <v>6.299699999999997E-2</v>
       </c>
       <c r="AC2" s="2">
-        <v>6.2230000000000008E-2</v>
+        <v>5.815300000000001E-2</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>96</v>
@@ -1211,181 +1190,181 @@
         <v>101</v>
       </c>
       <c r="AJ2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AM2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AO2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AV2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="BM2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="CB2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV2" s="2" t="s">
+      <c r="CE2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CG2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="CH2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CI2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CJ2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CK2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AX2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BS2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU2" s="2" t="s">
+      <c r="CM2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CN2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="CH2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CK2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CL2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CM2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="CN2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO2" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="CP2" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/f0de2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/Pikf1G/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{056DAA92-D8BD-1B4D-8041-79539E0BF11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B27A01D2-95CD-A84D-B5EC-037E179BCD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26200" yWindow="9200" windowWidth="27700" windowHeight="16860" xr2:uid="{A3C77F66-9BE8-F84F-9382-2D1C6E93537B}"/>
+    <workbookView xWindow="11940" yWindow="5940" windowWidth="27700" windowHeight="16860" xr2:uid="{34AD2F84-83C3-C141-8CBD-BF2566896881}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
   <si>
     <t>Folder Name</t>
   </si>
@@ -320,25 +320,25 @@
     <t>nf_M1</t>
   </si>
   <si>
-    <t>tmp_20241106043301135015506_tt</t>
+    <t>tmp_20241106223441403837171_tt</t>
   </si>
   <si>
     <t>tt</t>
   </si>
   <si>
-    <t>7.6p</t>
+    <t>8.9p</t>
   </si>
   <si>
     <t>0.1p</t>
   </si>
   <si>
-    <t>9.7p</t>
+    <t>6.3p</t>
   </si>
   <si>
     <t>1.75u</t>
   </si>
   <si>
-    <t>400.0k</t>
+    <t>100.0k</t>
   </si>
   <si>
     <t>0.25u</t>
@@ -347,46 +347,55 @@
     <t>1</t>
   </si>
   <si>
-    <t>9.5u</t>
+    <t>5.0u</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
+    <t>7.5u</t>
+  </si>
+  <si>
     <t>10.0u</t>
   </si>
   <si>
+    <t>1.25u</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>15.0u</t>
+  </si>
+  <si>
+    <t>60.0n</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9.25u</t>
+  </si>
+  <si>
+    <t>3.75u</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
+    <t>5.25u</t>
+  </si>
+  <si>
+    <t>2.5u</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>6.75u</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>15.0u</t>
-  </si>
-  <si>
-    <t>60.0n</t>
-  </si>
-  <si>
-    <t>7.5u</t>
-  </si>
-  <si>
-    <t>4.25u</t>
-  </si>
-  <si>
-    <t>8.75u</t>
-  </si>
-  <si>
-    <t>9.75u</t>
+    <t>6.5u</t>
   </si>
 </sst>
 </file>
@@ -795,7 +804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC731451-4C3A-7B44-8EFD-D9D7F44CF749}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CBFACE8-A593-AC40-94BC-23BF32161351}">
   <dimension ref="A1:CP2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
@@ -1091,85 +1100,85 @@
         <v>95</v>
       </c>
       <c r="C2" s="2">
-        <v>-6.3988800238670193E-2</v>
+        <v>-3.7771138245132001E-2</v>
       </c>
       <c r="D2" s="2">
-        <v>7.4068099999999998E-6</v>
+        <v>8.4865799999999996E-6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.953333333333251E-3</v>
+        <v>2.9133333333332249E-3</v>
       </c>
       <c r="F2" s="2">
-        <v>1.5911111111110989E-3</v>
+        <v>2.9399999999999179E-3</v>
       </c>
       <c r="G2" s="2">
-        <v>1.660700000000001</v>
+        <v>1.8686868686867749E-3</v>
       </c>
       <c r="H2" s="2">
-        <v>53.434802469729092</v>
+        <v>50.255889795841547</v>
       </c>
       <c r="I2" s="2">
-        <v>50.089611247586333</v>
+        <v>49.955436543641198</v>
       </c>
       <c r="J2" s="2">
-        <v>33.651478980556831</v>
+        <v>41.792735649183463</v>
       </c>
       <c r="K2" s="2">
-        <v>14.951439551350621</v>
+        <v>21.399975337222621</v>
       </c>
       <c r="L2" s="2">
-        <v>4.001817903512884</v>
+        <v>4.8880055914905656</v>
       </c>
       <c r="M2" s="2">
-        <v>55.355915407251601</v>
+        <v>50.055165632848841</v>
       </c>
       <c r="N2" s="2">
-        <v>50.967479251408257</v>
+        <v>49.773595789758367</v>
       </c>
       <c r="O2" s="2">
-        <v>33.805437219526993</v>
+        <v>41.840569170372937</v>
       </c>
       <c r="P2" s="2">
-        <v>15.040982564138529</v>
+        <v>21.464357676674869</v>
       </c>
       <c r="Q2" s="2">
-        <v>4.4498203777529746</v>
+        <v>5.1001637453811739</v>
       </c>
       <c r="R2" s="2">
-        <v>97.535510000000002</v>
+        <v>83.53716</v>
       </c>
       <c r="S2" s="2">
-        <v>235298.5</v>
+        <v>639657.1</v>
       </c>
       <c r="T2" s="2">
-        <v>106.86020000000001</v>
+        <v>86.11636</v>
       </c>
       <c r="U2" s="2">
-        <v>200315.1</v>
+        <v>681571.5</v>
       </c>
       <c r="V2" s="2">
-        <v>99.991349999999997</v>
+        <v>84.589889999999997</v>
       </c>
       <c r="W2" s="2">
-        <v>171402.4</v>
+        <v>617404.9</v>
       </c>
       <c r="X2" s="2">
-        <v>108.1123</v>
+        <v>86.360529999999997</v>
       </c>
       <c r="Y2" s="2">
-        <v>202191.2</v>
+        <v>692457.2</v>
       </c>
       <c r="Z2" s="2">
-        <v>8.8400999999999952E-2</v>
+        <v>8.8274546032609008E-2</v>
       </c>
       <c r="AA2" s="2">
-        <v>6.920599999999999E-2</v>
+        <v>7.5407303837713657E-2</v>
       </c>
       <c r="AB2" s="2">
-        <v>6.299699999999997E-2</v>
+        <v>6.8365490213547306E-2</v>
       </c>
       <c r="AC2" s="2">
-        <v>5.815300000000001E-2</v>
+        <v>6.6513789801101258E-2</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>96</v>
@@ -1211,52 +1220,52 @@
         <v>101</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AS2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="AT2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AU2" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="AV2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="AW2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AY2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AY2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="BA2" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="BB2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="BE2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BG2" s="2" t="s">
         <v>101</v>
@@ -1265,16 +1274,16 @@
         <v>101</v>
       </c>
       <c r="BI2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="BM2" s="2" t="s">
         <v>113</v>
@@ -1283,7 +1292,7 @@
         <v>114</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="BP2" s="2" t="s">
         <v>113</v>
@@ -1292,34 +1301,34 @@
         <v>114</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="BT2" s="2" t="s">
         <v>116</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="BW2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="BZ2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="CB2" s="2" t="s">
         <v>113</v>
@@ -1328,7 +1337,7 @@
         <v>114</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="CE2" s="2" t="s">
         <v>113</v>
@@ -1337,7 +1346,7 @@
         <v>114</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="CH2" s="2" t="s">
         <v>113</v>
@@ -1346,22 +1355,22 @@
         <v>114</v>
       </c>
       <c r="CJ2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="CK2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CL2" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="CK2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="CL2" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="CM2" s="2" t="s">
         <v>104</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="CP2" s="2" t="s">
         <v>104</v>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/Pikf1G/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B27A01D2-95CD-A84D-B5EC-037E179BCD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF9C018-80C4-9E47-8E81-41A85B785C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11940" yWindow="5940" windowWidth="27700" windowHeight="16860" xr2:uid="{34AD2F84-83C3-C141-8CBD-BF2566896881}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
   <si>
     <t>Folder Name</t>
   </si>
@@ -320,21 +320,12 @@
     <t>nf_M1</t>
   </si>
   <si>
-    <t>tmp_20241106223441403837171_tt</t>
-  </si>
-  <si>
     <t>tt</t>
   </si>
   <si>
-    <t>8.9p</t>
-  </si>
-  <si>
     <t>0.1p</t>
   </si>
   <si>
-    <t>6.3p</t>
-  </si>
-  <si>
     <t>1.75u</t>
   </si>
   <si>
@@ -347,24 +338,15 @@
     <t>1</t>
   </si>
   <si>
-    <t>5.0u</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>7.5u</t>
-  </si>
-  <si>
     <t>10.0u</t>
   </si>
   <si>
-    <t>1.25u</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -377,25 +359,34 @@
     <t>8</t>
   </si>
   <si>
-    <t>9.25u</t>
-  </si>
-  <si>
-    <t>3.75u</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
-    <t>5.25u</t>
-  </si>
-  <si>
-    <t>2.5u</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
-    <t>6.5u</t>
+    <t>tmp_20241107082303403909520_tt</t>
+  </si>
+  <si>
+    <t>8.6p</t>
+  </si>
+  <si>
+    <t>6.0p</t>
+  </si>
+  <si>
+    <t>4.75u</t>
+  </si>
+  <si>
+    <t>8.25u</t>
+  </si>
+  <si>
+    <t>3.5u</t>
+  </si>
+  <si>
+    <t>1.0u</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -807,6 +798,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CBFACE8-A593-AC40-94BC-23BF32161351}">
   <dimension ref="A1:CP2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:94" s="2" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -1094,286 +1088,286 @@
     </row>
     <row r="2" spans="1:94" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2">
+        <v>-4.5356321718820397E-2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>8.7639499999999993E-6</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3.1711111111110139E-3</v>
+      </c>
+      <c r="F2" s="2">
+        <v>3.251111111111094E-3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2.040404040404399E-3</v>
+      </c>
+      <c r="H2" s="2">
+        <v>50.207347020066067</v>
+      </c>
+      <c r="I2" s="2">
+        <v>49.967893600020247</v>
+      </c>
+      <c r="J2" s="2">
+        <v>42.599066924356563</v>
+      </c>
+      <c r="K2" s="2">
+        <v>22.336348949481039</v>
+      </c>
+      <c r="L2" s="2">
+        <v>6.8301495711323801</v>
+      </c>
+      <c r="M2" s="2">
+        <v>49.705520925867113</v>
+      </c>
+      <c r="N2" s="2">
+        <v>49.494910036051067</v>
+      </c>
+      <c r="O2" s="2">
+        <v>42.564146563398957</v>
+      </c>
+      <c r="P2" s="2">
+        <v>22.379497632297969</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>7.0725705526686138</v>
+      </c>
+      <c r="R2" s="2">
+        <v>94.449169999999995</v>
+      </c>
+      <c r="S2" s="2">
+        <v>719092.4</v>
+      </c>
+      <c r="T2" s="2">
+        <v>94.956159999999997</v>
+      </c>
+      <c r="U2" s="2">
+        <v>785325.8</v>
+      </c>
+      <c r="V2" s="2">
+        <v>94.71584</v>
+      </c>
+      <c r="W2" s="2">
+        <v>600054.5</v>
+      </c>
+      <c r="X2" s="2">
+        <v>95.247540000000001</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>814452.6</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>8.1172388919601227E-2</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>6.9877688854093858E-2</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>6.5364608114746564E-2</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>6.4866837865388646E-2</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="2">
-        <v>-3.7771138245132001E-2</v>
-      </c>
-      <c r="D2" s="2">
-        <v>8.4865799999999996E-6</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2.9133333333332249E-3</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2.9399999999999179E-3</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1.8686868686867749E-3</v>
-      </c>
-      <c r="H2" s="2">
-        <v>50.255889795841547</v>
-      </c>
-      <c r="I2" s="2">
-        <v>49.955436543641198</v>
-      </c>
-      <c r="J2" s="2">
-        <v>41.792735649183463</v>
-      </c>
-      <c r="K2" s="2">
-        <v>21.399975337222621</v>
-      </c>
-      <c r="L2" s="2">
-        <v>4.8880055914905656</v>
-      </c>
-      <c r="M2" s="2">
-        <v>50.055165632848841</v>
-      </c>
-      <c r="N2" s="2">
-        <v>49.773595789758367</v>
-      </c>
-      <c r="O2" s="2">
-        <v>41.840569170372937</v>
-      </c>
-      <c r="P2" s="2">
-        <v>21.464357676674869</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>5.1001637453811739</v>
-      </c>
-      <c r="R2" s="2">
-        <v>83.53716</v>
-      </c>
-      <c r="S2" s="2">
-        <v>639657.1</v>
-      </c>
-      <c r="T2" s="2">
-        <v>86.11636</v>
-      </c>
-      <c r="U2" s="2">
-        <v>681571.5</v>
-      </c>
-      <c r="V2" s="2">
-        <v>84.589889999999997</v>
-      </c>
-      <c r="W2" s="2">
-        <v>617404.9</v>
-      </c>
-      <c r="X2" s="2">
-        <v>86.360529999999997</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>692457.2</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>8.8274546032609008E-2</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>7.5407303837713657E-2</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>6.8365490213547306E-2</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>6.6513789801101258E-2</v>
-      </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="AF2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AI2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AM2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AN2" s="2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="BN2" s="2" t="s">
         <v>114</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BQ2" s="2" t="s">
         <v>114</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BU2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="CB2" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="BV2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="CC2" s="2" t="s">
         <v>114</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="CF2" s="2" t="s">
         <v>114</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="CI2" s="2" t="s">
         <v>114</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/Pikf1G/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF9C018-80C4-9E47-8E81-41A85B785C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E72780-0C0A-6C46-BE15-0C6BA752D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11940" yWindow="5940" windowWidth="27700" windowHeight="16860" xr2:uid="{34AD2F84-83C3-C141-8CBD-BF2566896881}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
   <si>
     <t>Folder Name</t>
   </si>
@@ -326,9 +326,6 @@
     <t>0.1p</t>
   </si>
   <si>
-    <t>1.75u</t>
-  </si>
-  <si>
     <t>100.0k</t>
   </si>
   <si>
@@ -365,21 +362,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>tmp_20241107082303403909520_tt</t>
-  </si>
-  <si>
-    <t>8.6p</t>
-  </si>
-  <si>
-    <t>6.0p</t>
-  </si>
-  <si>
-    <t>4.75u</t>
-  </si>
-  <si>
-    <t>8.25u</t>
-  </si>
-  <si>
     <t>3.5u</t>
   </si>
   <si>
@@ -387,6 +369,33 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>tmp_20241106214051298442815_tt</t>
+  </si>
+  <si>
+    <t>5.6p</t>
+  </si>
+  <si>
+    <t>10.0p</t>
+  </si>
+  <si>
+    <t>1.5u</t>
+  </si>
+  <si>
+    <t>9.0u</t>
+  </si>
+  <si>
+    <t>5.0u</t>
+  </si>
+  <si>
+    <t>6.0u</t>
+  </si>
+  <si>
+    <t>0.75u</t>
+  </si>
+  <si>
+    <t>7.5u</t>
   </si>
 </sst>
 </file>
@@ -1088,286 +1097,286 @@
     </row>
     <row r="2" spans="1:94" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C2" s="2">
-        <v>-4.5356321718820397E-2</v>
+        <v>-0.13396503367960261</v>
       </c>
       <c r="D2" s="2">
-        <v>8.7639499999999993E-6</v>
+        <v>7.9802000000000003E-6</v>
       </c>
       <c r="E2" s="2">
-        <v>3.1711111111110139E-3</v>
+        <v>6.1155555555555043E-3</v>
       </c>
       <c r="F2" s="2">
-        <v>3.251111111111094E-3</v>
+        <v>6.0133333333333028E-3</v>
       </c>
       <c r="G2" s="2">
-        <v>2.040404040404399E-3</v>
+        <v>2.3131313131316642E-3</v>
       </c>
       <c r="H2" s="2">
-        <v>50.207347020066067</v>
+        <v>44.166937062511742</v>
       </c>
       <c r="I2" s="2">
-        <v>49.967893600020247</v>
+        <v>43.960820641426153</v>
       </c>
       <c r="J2" s="2">
-        <v>42.599066924356563</v>
+        <v>37.098808616655937</v>
       </c>
       <c r="K2" s="2">
-        <v>22.336348949481039</v>
+        <v>16.506452933174518</v>
       </c>
       <c r="L2" s="2">
-        <v>6.8301495711323801</v>
+        <v>3.109608745353833</v>
       </c>
       <c r="M2" s="2">
-        <v>49.705520925867113</v>
+        <v>43.875884255059553</v>
       </c>
       <c r="N2" s="2">
-        <v>49.494910036051067</v>
+        <v>43.685430680452662</v>
       </c>
       <c r="O2" s="2">
-        <v>42.564146563398957</v>
+        <v>37.087190870639724</v>
       </c>
       <c r="P2" s="2">
-        <v>22.379497632297969</v>
+        <v>16.518520929826149</v>
       </c>
       <c r="Q2" s="2">
-        <v>7.0725705526686138</v>
+        <v>3.5450091076631511</v>
       </c>
       <c r="R2" s="2">
-        <v>94.449169999999995</v>
+        <v>77.493160000000003</v>
       </c>
       <c r="S2" s="2">
-        <v>719092.4</v>
+        <v>427046.40000000002</v>
       </c>
       <c r="T2" s="2">
-        <v>94.956159999999997</v>
+        <v>79.15128</v>
       </c>
       <c r="U2" s="2">
-        <v>785325.8</v>
+        <v>462823.5</v>
       </c>
       <c r="V2" s="2">
-        <v>94.71584</v>
+        <v>79.078530000000001</v>
       </c>
       <c r="W2" s="2">
-        <v>600054.5</v>
+        <v>416775.9</v>
       </c>
       <c r="X2" s="2">
-        <v>95.247540000000001</v>
+        <v>80.189030000000002</v>
       </c>
       <c r="Y2" s="2">
-        <v>814452.6</v>
+        <v>477744.8</v>
       </c>
       <c r="Z2" s="2">
-        <v>8.1172388919601227E-2</v>
+        <v>0.1142320382515354</v>
       </c>
       <c r="AA2" s="2">
-        <v>6.9877688854093858E-2</v>
+        <v>8.0427534514619856E-2</v>
       </c>
       <c r="AB2" s="2">
-        <v>6.5364608114746564E-2</v>
+        <v>9.4300350425203239E-2</v>
       </c>
       <c r="AC2" s="2">
-        <v>6.4866837865388646E-2</v>
+        <v>7.6378404930764213E-2</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>95</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="AL2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AQ2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AR2" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="AS2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AT2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AU2" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="AV2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AW2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AX2" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="AY2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BC2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BF2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BM2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="BM2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BP2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="BS2" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="CA2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="CG2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="CH2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="CH2" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="CI2" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="CK2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CL2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CM2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CN2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CO2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CP2" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="CM2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="CN2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="CO2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="CP2" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/Pikf1G/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/Di8uCk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E72780-0C0A-6C46-BE15-0C6BA752D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{614FDC49-4E26-8943-84C5-C3E186B41C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11940" yWindow="5940" windowWidth="27700" windowHeight="16860" xr2:uid="{34AD2F84-83C3-C141-8CBD-BF2566896881}"/>
+    <workbookView xWindow="-28480" yWindow="12840" windowWidth="27700" windowHeight="16860" xr2:uid="{9A2E230D-01E3-A847-9D00-B419379C98AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="128">
   <si>
     <t>Folder Name</t>
   </si>
@@ -320,82 +320,106 @@
     <t>nf_M1</t>
   </si>
   <si>
+    <t>tmp_20241107224812200875413_tt</t>
+  </si>
+  <si>
     <t>tt</t>
   </si>
   <si>
+    <t>7.6p</t>
+  </si>
+  <si>
     <t>0.1p</t>
   </si>
   <si>
+    <t>10.0p</t>
+  </si>
+  <si>
+    <t>1.5u</t>
+  </si>
+  <si>
+    <t>200.0k</t>
+  </si>
+  <si>
+    <t>0.25u</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>7.75u</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>8.0u</t>
+  </si>
+  <si>
+    <t>10.0u</t>
+  </si>
+  <si>
+    <t>9.75u</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>15.0u</t>
+  </si>
+  <si>
+    <t>60.0n</t>
+  </si>
+  <si>
+    <t>8.5u</t>
+  </si>
+  <si>
+    <t>3.75u</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8.75u</t>
+  </si>
+  <si>
+    <t>2.75u</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>9.25u</t>
+  </si>
+  <si>
+    <t>tmp_20241107195557208921726_tt</t>
+  </si>
+  <si>
+    <t>9.3p</t>
+  </si>
+  <si>
     <t>100.0k</t>
   </si>
   <si>
-    <t>0.25u</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10.0u</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>15.0u</t>
-  </si>
-  <si>
-    <t>60.0n</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>5.25u</t>
+  </si>
+  <si>
+    <t>5.5u</t>
   </si>
   <si>
     <t>3.5u</t>
   </si>
   <si>
-    <t>1.0u</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>tmp_20241106214051298442815_tt</t>
-  </si>
-  <si>
-    <t>5.6p</t>
-  </si>
-  <si>
-    <t>10.0p</t>
-  </si>
-  <si>
-    <t>1.5u</t>
-  </si>
-  <si>
-    <t>9.0u</t>
-  </si>
-  <si>
-    <t>5.0u</t>
-  </si>
-  <si>
-    <t>6.0u</t>
-  </si>
-  <si>
-    <t>0.75u</t>
-  </si>
-  <si>
-    <t>7.5u</t>
+    <t>6.5u</t>
+  </si>
+  <si>
+    <t>1.25u</t>
   </si>
 </sst>
 </file>
@@ -804,12 +828,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CBFACE8-A593-AC40-94BC-23BF32161351}">
-  <dimension ref="A1:CP2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BADE93AF-C294-F641-8263-893439A1591A}">
+  <dimension ref="A1:CP3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="32.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:94" s="2" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -1097,286 +1118,570 @@
     </row>
     <row r="2" spans="1:94" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2">
-        <v>-0.13396503367960261</v>
+        <v>-3.8102637013379299E-2</v>
       </c>
       <c r="D2" s="2">
-        <v>7.9802000000000003E-6</v>
+        <v>8.0745700000000002E-6</v>
       </c>
       <c r="E2" s="2">
-        <v>6.1155555555555043E-3</v>
+        <v>4.5688888888887709E-3</v>
       </c>
       <c r="F2" s="2">
-        <v>6.0133333333333028E-3</v>
+        <v>4.528888888888854E-3</v>
       </c>
       <c r="G2" s="2">
-        <v>2.3131313131316642E-3</v>
+        <v>2.101010101011081E-3</v>
       </c>
       <c r="H2" s="2">
-        <v>44.166937062511742</v>
+        <v>46.722461348401723</v>
       </c>
       <c r="I2" s="2">
-        <v>43.960820641426153</v>
+        <v>46.361761736321178</v>
       </c>
       <c r="J2" s="2">
-        <v>37.098808616655937</v>
+        <v>37.549917188087719</v>
       </c>
       <c r="K2" s="2">
-        <v>16.506452933174518</v>
+        <v>17.322705850048798</v>
       </c>
       <c r="L2" s="2">
-        <v>3.109608745353833</v>
+        <v>4.9523190003016593</v>
       </c>
       <c r="M2" s="2">
-        <v>43.875884255059553</v>
+        <v>46.44202268028593</v>
       </c>
       <c r="N2" s="2">
-        <v>43.685430680452662</v>
+        <v>46.108846904256211</v>
       </c>
       <c r="O2" s="2">
-        <v>37.087190870639724</v>
+        <v>37.581960378947919</v>
       </c>
       <c r="P2" s="2">
-        <v>16.518520929826149</v>
+        <v>17.360847540249431</v>
       </c>
       <c r="Q2" s="2">
-        <v>3.5450091076631511</v>
+        <v>5.3423266987152971</v>
       </c>
       <c r="R2" s="2">
-        <v>77.493160000000003</v>
+        <v>92.941400000000002</v>
       </c>
       <c r="S2" s="2">
-        <v>427046.40000000002</v>
+        <v>418204.9</v>
       </c>
       <c r="T2" s="2">
-        <v>79.15128</v>
+        <v>94.275710000000004</v>
       </c>
       <c r="U2" s="2">
-        <v>462823.5</v>
+        <v>467907.4</v>
       </c>
       <c r="V2" s="2">
-        <v>79.078530000000001</v>
+        <v>93.695520000000002</v>
       </c>
       <c r="W2" s="2">
-        <v>416775.9</v>
+        <v>408812.1</v>
       </c>
       <c r="X2" s="2">
-        <v>80.189030000000002</v>
+        <v>94.677809999999994</v>
       </c>
       <c r="Y2" s="2">
-        <v>477744.8</v>
+        <v>484146.2</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1142320382515354</v>
+        <v>0.109477</v>
       </c>
       <c r="AA2" s="2">
-        <v>8.0427534514619856E-2</v>
+        <v>7.0969999999999978E-2</v>
       </c>
       <c r="AB2" s="2">
-        <v>9.4300350425203239E-2</v>
+        <v>8.3729999999999971E-2</v>
       </c>
       <c r="AC2" s="2">
-        <v>7.6378404930764213E-2</v>
+        <v>5.9354000000000018E-2</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AI2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AJ2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AP2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="BG2" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="BI2" s="2" t="s">
         <v>110</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="BK2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="BL2" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="BM2" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BS2" s="2" t="s">
         <v>116</v>
       </c>
       <c r="BT2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="BU2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BW2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="BW2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BY2" s="2" t="s">
+      <c r="CE2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CG2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CH2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CI2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CJ2" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="CK2" s="2" t="s">
         <v>119</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="CN2" s="2" t="s">
         <v>119</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="CP2" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:94" s="2" customFormat="1">
+      <c r="A3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-6.1105447448742502E-2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>7.6317899999999997E-6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5.3911111111111989E-3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5.4022222222223828E-3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.7171717171717521E-3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>45.191782587727893</v>
+      </c>
+      <c r="I3" s="2">
+        <v>44.949091133629707</v>
+      </c>
+      <c r="J3" s="2">
+        <v>37.531452874832517</v>
+      </c>
+      <c r="K3" s="2">
+        <v>17.03526860940562</v>
+      </c>
+      <c r="L3" s="2">
+        <v>4.6622085490072589</v>
+      </c>
+      <c r="M3" s="2">
+        <v>44.985570505390598</v>
+      </c>
+      <c r="N3" s="2">
+        <v>44.756472936629557</v>
+      </c>
+      <c r="O3" s="2">
+        <v>37.53661357118898</v>
+      </c>
+      <c r="P3" s="2">
+        <v>17.028969882334241</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5.1648879935433998</v>
+      </c>
+      <c r="R3" s="2">
+        <v>32.416379999999997</v>
+      </c>
+      <c r="S3" s="2">
+        <v>3963930</v>
+      </c>
+      <c r="T3" s="2">
+        <v>89.105289999999997</v>
+      </c>
+      <c r="U3" s="2">
+        <v>473227.1</v>
+      </c>
+      <c r="V3" s="2">
+        <v>23.502970000000001</v>
+      </c>
+      <c r="W3" s="2">
+        <v>3991820</v>
+      </c>
+      <c r="X3" s="2">
+        <v>89.912570000000002</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>498446.5</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.11225300000000001</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>7.027899999999998E-2</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>8.7641999999999998E-2</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>6.1674000000000007E-2</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>102</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/Di8uCk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/fEqCIN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{614FDC49-4E26-8943-84C5-C3E186B41C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0032132-1552-A14D-8A7B-CBEB149B172B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28480" yWindow="12840" windowWidth="27700" windowHeight="16860" xr2:uid="{9A2E230D-01E3-A847-9D00-B419379C98AE}"/>
+    <workbookView xWindow="3120" yWindow="9100" windowWidth="27700" windowHeight="16860" xr2:uid="{75B7FA8E-E8D8-FE49-A324-FB65C9F5A3C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="121">
   <si>
     <t>Folder Name</t>
   </si>
@@ -320,25 +320,25 @@
     <t>nf_M1</t>
   </si>
   <si>
-    <t>tmp_20241107224812200875413_tt</t>
+    <t>tmp_20241111150920561448606_tt</t>
   </si>
   <si>
     <t>tt</t>
   </si>
   <si>
-    <t>7.6p</t>
+    <t>6.7p</t>
   </si>
   <si>
     <t>0.1p</t>
   </si>
   <si>
-    <t>10.0p</t>
-  </si>
-  <si>
-    <t>1.5u</t>
-  </si>
-  <si>
-    <t>200.0k</t>
+    <t>2.4p</t>
+  </si>
+  <si>
+    <t>1.75u</t>
+  </si>
+  <si>
+    <t>100.0k</t>
   </si>
   <si>
     <t>0.25u</t>
@@ -347,86 +347,65 @@
     <t>1</t>
   </si>
   <si>
+    <t>8.5u</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10.0u</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>8.0u</t>
+  </si>
+  <si>
+    <t>6.25u</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>15.0u</t>
+  </si>
+  <si>
+    <t>60.0n</t>
+  </si>
+  <si>
+    <t>5.75u</t>
+  </si>
+  <si>
+    <t>4.0u</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>7.75u</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>8.0u</t>
-  </si>
-  <si>
-    <t>10.0u</t>
-  </si>
-  <si>
-    <t>9.75u</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>2.75u</t>
+  </si>
+  <si>
+    <t>3.0u</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>15.0u</t>
-  </si>
-  <si>
-    <t>60.0n</t>
-  </si>
-  <si>
-    <t>8.5u</t>
-  </si>
-  <si>
-    <t>3.75u</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8.75u</t>
-  </si>
-  <si>
-    <t>2.75u</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>9.25u</t>
-  </si>
-  <si>
-    <t>tmp_20241107195557208921726_tt</t>
-  </si>
-  <si>
-    <t>9.3p</t>
-  </si>
-  <si>
-    <t>100.0k</t>
-  </si>
-  <si>
-    <t>5.25u</t>
-  </si>
-  <si>
-    <t>5.5u</t>
-  </si>
-  <si>
-    <t>3.5u</t>
-  </si>
-  <si>
-    <t>6.5u</t>
-  </si>
-  <si>
-    <t>1.25u</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -448,6 +427,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -487,7 +473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -495,6 +481,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -828,7 +817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BADE93AF-C294-F641-8263-893439A1591A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C9FDA6-E018-BB45-9E12-FF2210F3FEFA}">
   <dimension ref="A1:CP3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
@@ -1124,85 +1113,85 @@
         <v>95</v>
       </c>
       <c r="C2" s="2">
-        <v>-3.8102637013379299E-2</v>
+        <v>14.106633521377899</v>
       </c>
       <c r="D2" s="2">
-        <v>8.0745700000000002E-6</v>
+        <v>7.9872000000000004E-6</v>
       </c>
       <c r="E2" s="2">
-        <v>4.5688888888887709E-3</v>
+        <v>8.6666666666691673E-5</v>
       </c>
       <c r="F2" s="2">
-        <v>4.528888888888854E-3</v>
+        <v>1.333333333334667E-4</v>
       </c>
       <c r="G2" s="2">
-        <v>2.101010101011081E-3</v>
+        <v>1.9898989898978958E-3</v>
       </c>
       <c r="H2" s="2">
-        <v>46.722461348401723</v>
+        <v>84.365331294793492</v>
       </c>
       <c r="I2" s="2">
-        <v>46.361761736321178</v>
+        <v>69.548347014144895</v>
       </c>
       <c r="J2" s="2">
-        <v>37.549917188087719</v>
+        <v>50.445033433284252</v>
       </c>
       <c r="K2" s="2">
-        <v>17.322705850048798</v>
+        <v>29.289671113255249</v>
       </c>
       <c r="L2" s="2">
-        <v>4.9523190003016593</v>
+        <v>11.33608804264027</v>
       </c>
       <c r="M2" s="2">
-        <v>46.44202268028593</v>
+        <v>88.45341151727402</v>
       </c>
       <c r="N2" s="2">
-        <v>46.108846904256211</v>
+        <v>69.717645937420457</v>
       </c>
       <c r="O2" s="2">
-        <v>37.581960378947919</v>
+        <v>50.528098120533443</v>
       </c>
       <c r="P2" s="2">
-        <v>17.360847540249431</v>
+        <v>29.36045086964749</v>
       </c>
       <c r="Q2" s="2">
-        <v>5.3423266987152971</v>
+        <v>11.419250146723099</v>
       </c>
       <c r="R2" s="2">
-        <v>92.941400000000002</v>
+        <v>88.966719999999995</v>
       </c>
       <c r="S2" s="2">
-        <v>418204.9</v>
+        <v>1854995</v>
       </c>
       <c r="T2" s="2">
-        <v>94.275710000000004</v>
+        <v>87.659260000000003</v>
       </c>
       <c r="U2" s="2">
-        <v>467907.4</v>
+        <v>2087974</v>
       </c>
       <c r="V2" s="2">
-        <v>93.695520000000002</v>
+        <v>89.78013</v>
       </c>
       <c r="W2" s="2">
-        <v>408812.1</v>
+        <v>1771443</v>
       </c>
       <c r="X2" s="2">
-        <v>94.677809999999994</v>
+        <v>85.784559999999999</v>
       </c>
       <c r="Y2" s="2">
-        <v>484146.2</v>
+        <v>2149247</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.109477</v>
+        <v>9.136500000000003E-2</v>
       </c>
       <c r="AA2" s="2">
-        <v>7.0969999999999978E-2</v>
+        <v>6.9754000000000038E-2</v>
       </c>
       <c r="AB2" s="2">
-        <v>8.3729999999999971E-2</v>
+        <v>7.1340999999999988E-2</v>
       </c>
       <c r="AC2" s="2">
-        <v>5.9354000000000018E-2</v>
+        <v>6.1796000000000018E-2</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>96</v>
@@ -1253,7 +1242,7 @@
         <v>101</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AU2" s="2" t="s">
         <v>106</v>
@@ -1265,31 +1254,31 @@
         <v>105</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AY2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="BC2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BD2" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="BE2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BG2" s="2" t="s">
         <v>101</v>
@@ -1307,7 +1296,7 @@
         <v>112</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BM2" s="2" t="s">
         <v>113</v>
@@ -1331,13 +1320,13 @@
         <v>116</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BW2" s="2" t="s">
         <v>101</v>
@@ -1346,13 +1335,13 @@
         <v>105</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BZ2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="CB2" s="2" t="s">
         <v>113</v>
@@ -1361,7 +1350,7 @@
         <v>114</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="CE2" s="2" t="s">
         <v>113</v>
@@ -1379,310 +1368,122 @@
         <v>114</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:94" s="2" customFormat="1">
-      <c r="A3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-6.1105447448742502E-2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>7.6317899999999997E-6</v>
-      </c>
-      <c r="E3" s="2">
-        <v>5.3911111111111989E-3</v>
-      </c>
-      <c r="F3" s="2">
-        <v>5.4022222222223828E-3</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1.7171717171717521E-3</v>
-      </c>
-      <c r="H3" s="2">
-        <v>45.191782587727893</v>
-      </c>
-      <c r="I3" s="2">
-        <v>44.949091133629707</v>
-      </c>
-      <c r="J3" s="2">
-        <v>37.531452874832517</v>
-      </c>
-      <c r="K3" s="2">
-        <v>17.03526860940562</v>
-      </c>
-      <c r="L3" s="2">
-        <v>4.6622085490072589</v>
-      </c>
-      <c r="M3" s="2">
-        <v>44.985570505390598</v>
-      </c>
-      <c r="N3" s="2">
-        <v>44.756472936629557</v>
-      </c>
-      <c r="O3" s="2">
-        <v>37.53661357118898</v>
-      </c>
-      <c r="P3" s="2">
-        <v>17.028969882334241</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5.1648879935433998</v>
-      </c>
-      <c r="R3" s="2">
-        <v>32.416379999999997</v>
-      </c>
-      <c r="S3" s="2">
-        <v>3963930</v>
-      </c>
-      <c r="T3" s="2">
-        <v>89.105289999999997</v>
-      </c>
-      <c r="U3" s="2">
-        <v>473227.1</v>
-      </c>
-      <c r="V3" s="2">
-        <v>23.502970000000001</v>
-      </c>
-      <c r="W3" s="2">
-        <v>3991820</v>
-      </c>
-      <c r="X3" s="2">
-        <v>89.912570000000002</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>498446.5</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>0.11225300000000001</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>7.027899999999998E-2</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>8.7641999999999998E-2</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>6.1674000000000007E-2</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>118</v>
-      </c>
+    <row r="3" spans="1:94">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+      <c r="AO3" s="3"/>
+      <c r="AP3" s="3"/>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="AZ3" s="3"/>
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
+      <c r="BF3" s="3"/>
+      <c r="BG3" s="3"/>
+      <c r="BH3" s="3"/>
+      <c r="BI3" s="3"/>
+      <c r="BJ3" s="3"/>
+      <c r="BK3" s="3"/>
+      <c r="BL3" s="3"/>
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="3"/>
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
+      <c r="BR3" s="3"/>
+      <c r="BS3" s="3"/>
+      <c r="BT3" s="3"/>
+      <c r="BU3" s="3"/>
+      <c r="BV3" s="3"/>
+      <c r="BW3" s="3"/>
+      <c r="BX3" s="3"/>
+      <c r="BY3" s="3"/>
+      <c r="BZ3" s="3"/>
+      <c r="CA3" s="3"/>
+      <c r="CB3" s="3"/>
+      <c r="CC3" s="3"/>
+      <c r="CD3" s="3"/>
+      <c r="CE3" s="3"/>
+      <c r="CF3" s="3"/>
+      <c r="CG3" s="3"/>
+      <c r="CH3" s="3"/>
+      <c r="CI3" s="3"/>
+      <c r="CJ3" s="3"/>
+      <c r="CK3" s="3"/>
+      <c r="CL3" s="3"/>
+      <c r="CM3" s="3"/>
+      <c r="CN3" s="3"/>
+      <c r="CO3" s="3"/>
+      <c r="CP3" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/fEqCIN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0032132-1552-A14D-8A7B-CBEB149B172B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6327CE12-A97E-9140-88F4-ACCC73B9C031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="9100" windowWidth="27700" windowHeight="16860" xr2:uid="{75B7FA8E-E8D8-FE49-A324-FB65C9F5A3C0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="136">
   <si>
     <t>Folder Name</t>
   </si>
@@ -399,13 +399,58 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>tmp_20241111160744559219309_tt</t>
+  </si>
+  <si>
+    <t>7.1p</t>
+  </si>
+  <si>
+    <t>2.2p</t>
+  </si>
+  <si>
+    <t>9.75u</t>
+  </si>
+  <si>
+    <t>5.5u</t>
+  </si>
+  <si>
+    <t>3.75u</t>
+  </si>
+  <si>
+    <t>1.5u</t>
+  </si>
+  <si>
+    <t>2.5u</t>
+  </si>
+  <si>
+    <t>tmp_20241111153213569309694_tt</t>
+  </si>
+  <si>
+    <t>2.0p</t>
+  </si>
+  <si>
+    <t>2.0u</t>
+  </si>
+  <si>
+    <t>4.25u</t>
+  </si>
+  <si>
+    <t>9.5u</t>
+  </si>
+  <si>
+    <t>2.25u</t>
+  </si>
+  <si>
+    <t>3.5u</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -427,13 +472,6 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -473,7 +511,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -481,9 +519,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -818,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C9FDA6-E018-BB45-9E12-FF2210F3FEFA}">
-  <dimension ref="A1:CP3"/>
+  <dimension ref="A1:CP4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:94" s="2" customFormat="1">
@@ -1389,101 +1424,573 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:94">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
-      <c r="AT3" s="3"/>
-      <c r="AU3" s="3"/>
-      <c r="AV3" s="3"/>
-      <c r="AW3" s="3"/>
-      <c r="AX3" s="3"/>
-      <c r="AY3" s="3"/>
-      <c r="AZ3" s="3"/>
-      <c r="BA3" s="3"/>
-      <c r="BB3" s="3"/>
-      <c r="BC3" s="3"/>
-      <c r="BD3" s="3"/>
-      <c r="BE3" s="3"/>
-      <c r="BF3" s="3"/>
-      <c r="BG3" s="3"/>
-      <c r="BH3" s="3"/>
-      <c r="BI3" s="3"/>
-      <c r="BJ3" s="3"/>
-      <c r="BK3" s="3"/>
-      <c r="BL3" s="3"/>
-      <c r="BM3" s="3"/>
-      <c r="BN3" s="3"/>
-      <c r="BO3" s="3"/>
-      <c r="BP3" s="3"/>
-      <c r="BQ3" s="3"/>
-      <c r="BR3" s="3"/>
-      <c r="BS3" s="3"/>
-      <c r="BT3" s="3"/>
-      <c r="BU3" s="3"/>
-      <c r="BV3" s="3"/>
-      <c r="BW3" s="3"/>
-      <c r="BX3" s="3"/>
-      <c r="BY3" s="3"/>
-      <c r="BZ3" s="3"/>
-      <c r="CA3" s="3"/>
-      <c r="CB3" s="3"/>
-      <c r="CC3" s="3"/>
-      <c r="CD3" s="3"/>
-      <c r="CE3" s="3"/>
-      <c r="CF3" s="3"/>
-      <c r="CG3" s="3"/>
-      <c r="CH3" s="3"/>
-      <c r="CI3" s="3"/>
-      <c r="CJ3" s="3"/>
-      <c r="CK3" s="3"/>
-      <c r="CL3" s="3"/>
-      <c r="CM3" s="3"/>
-      <c r="CN3" s="3"/>
-      <c r="CO3" s="3"/>
-      <c r="CP3" s="3"/>
+    <row r="3" spans="1:94" s="2" customFormat="1">
+      <c r="A3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-3.8559915473051001E-3</v>
+      </c>
+      <c r="D3" s="2">
+        <v>8.0703400000000007E-6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3.1444444444445668E-3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3.157777777777791E-3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.9292929292928961E-3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>49.885014644466338</v>
+      </c>
+      <c r="I3" s="2">
+        <v>49.844125296723007</v>
+      </c>
+      <c r="J3" s="2">
+        <v>47.342550168382651</v>
+      </c>
+      <c r="K3" s="2">
+        <v>29.72347035225426</v>
+      </c>
+      <c r="L3" s="2">
+        <v>11.74811821387982</v>
+      </c>
+      <c r="M3" s="2">
+        <v>49.677912669777967</v>
+      </c>
+      <c r="N3" s="2">
+        <v>49.639556069786053</v>
+      </c>
+      <c r="O3" s="2">
+        <v>47.257720767611247</v>
+      </c>
+      <c r="P3" s="2">
+        <v>29.78376552051505</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>11.82007791383038</v>
+      </c>
+      <c r="R3" s="2">
+        <v>85.845309999999998</v>
+      </c>
+      <c r="S3" s="2">
+        <v>2146060</v>
+      </c>
+      <c r="T3" s="2">
+        <v>88.091210000000004</v>
+      </c>
+      <c r="U3" s="2">
+        <v>2378135</v>
+      </c>
+      <c r="V3" s="2">
+        <v>87.740179999999995</v>
+      </c>
+      <c r="W3" s="2">
+        <v>2082712</v>
+      </c>
+      <c r="X3" s="2">
+        <v>86.935630000000003</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>2451974</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>8.5758999999999974E-2</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>6.7856000000000027E-2</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>6.8945000000000034E-2</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>6.0256000000000032E-2</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CC3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:94" s="2" customFormat="1">
+      <c r="A4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-4.8083561684613002E-3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8.0991199999999998E-6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5.8222222222218778E-4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6.5111111111108388E-4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.6969696969698712E-3</v>
+      </c>
+      <c r="H4" s="2">
+        <v>66.789292786619711</v>
+      </c>
+      <c r="I4" s="2">
+        <v>65.279952056677544</v>
+      </c>
+      <c r="J4" s="2">
+        <v>51.232911148766149</v>
+      </c>
+      <c r="K4" s="2">
+        <v>30.26839973142059</v>
+      </c>
+      <c r="L4" s="2">
+        <v>12.402724392604149</v>
+      </c>
+      <c r="M4" s="2">
+        <v>65.331842924836067</v>
+      </c>
+      <c r="N4" s="2">
+        <v>64.222788556010187</v>
+      </c>
+      <c r="O4" s="2">
+        <v>51.272170175603407</v>
+      </c>
+      <c r="P4" s="2">
+        <v>30.34744866543496</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>12.482537912788381</v>
+      </c>
+      <c r="R4" s="2">
+        <v>92.859960000000001</v>
+      </c>
+      <c r="S4" s="2">
+        <v>2232089</v>
+      </c>
+      <c r="T4" s="2">
+        <v>92.156769999999995</v>
+      </c>
+      <c r="U4" s="2">
+        <v>2485515</v>
+      </c>
+      <c r="V4" s="2">
+        <v>93.997230000000002</v>
+      </c>
+      <c r="W4" s="2">
+        <v>2061732</v>
+      </c>
+      <c r="X4" s="2">
+        <v>90.980689999999996</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>2523386</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>9.1458000000000039E-2</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>6.6691999999999974E-2</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>7.179000000000002E-2</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>5.8847000000000038E-2</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BO4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BY4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BZ4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CA4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="CB4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CD4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CE4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CG4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CH4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CI4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CJ4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CK4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CL4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CM4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CN4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CO4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP4" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/custom_env/skill_util/Jianping/Select.xlsx
+++ b/custom_env/skill_util/Jianping/Select.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Desktop/Paper_Material/Train_Data/Jianping/fEqCIN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6327CE12-A97E-9140-88F4-ACCC73B9C031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8725ADF-973F-F042-8678-3D936467B333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="9100" windowWidth="27700" windowHeight="16860" xr2:uid="{75B7FA8E-E8D8-FE49-A324-FB65C9F5A3C0}"/>
+    <workbookView xWindow="-34000" yWindow="7160" windowWidth="27700" windowHeight="16860" xr2:uid="{75B7FA8E-E8D8-FE49-A324-FB65C9F5A3C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="179">
   <si>
     <t>Folder Name</t>
   </si>
@@ -320,21 +320,12 @@
     <t>nf_M1</t>
   </si>
   <si>
-    <t>tmp_20241111150920561448606_tt</t>
-  </si>
-  <si>
     <t>tt</t>
   </si>
   <si>
-    <t>6.7p</t>
-  </si>
-  <si>
     <t>0.1p</t>
   </si>
   <si>
-    <t>2.4p</t>
-  </si>
-  <si>
     <t>1.75u</t>
   </si>
   <si>
@@ -401,15 +392,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>tmp_20241111160744559219309_tt</t>
-  </si>
-  <si>
-    <t>7.1p</t>
-  </si>
-  <si>
-    <t>2.2p</t>
-  </si>
-  <si>
     <t>9.75u</t>
   </si>
   <si>
@@ -419,18 +401,9 @@
     <t>3.75u</t>
   </si>
   <si>
-    <t>1.5u</t>
-  </si>
-  <si>
     <t>2.5u</t>
   </si>
   <si>
-    <t>tmp_20241111153213569309694_tt</t>
-  </si>
-  <si>
-    <t>2.0p</t>
-  </si>
-  <si>
     <t>2.0u</t>
   </si>
   <si>
@@ -444,6 +417,162 @@
   </si>
   <si>
     <t>3.5u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130958557818402_tt</t>
+  </si>
+  <si>
+    <t>5.8p</t>
+  </si>
+  <si>
+    <t>10.0p</t>
+  </si>
+  <si>
+    <t>300.0k</t>
+  </si>
+  <si>
+    <t>7.5u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130958579213231_tt</t>
+  </si>
+  <si>
+    <t>8.8p</t>
+  </si>
+  <si>
+    <t>9.8p</t>
+  </si>
+  <si>
+    <t>200.0k</t>
+  </si>
+  <si>
+    <t>4.5u</t>
+  </si>
+  <si>
+    <t>4.75u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959557619523_tt</t>
+  </si>
+  <si>
+    <t>9.5p</t>
+  </si>
+  <si>
+    <t>5.25u</t>
+  </si>
+  <si>
+    <t>6.0u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959576852443_tt</t>
+  </si>
+  <si>
+    <t>8.4p</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>7.25u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959559157607_tt</t>
+  </si>
+  <si>
+    <t>9.4p</t>
+  </si>
+  <si>
+    <t>9.0u</t>
+  </si>
+  <si>
+    <t>8.75u</t>
+  </si>
+  <si>
+    <t>1.0u</t>
+  </si>
+  <si>
+    <t>1.25u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959557712839_tt</t>
+  </si>
+  <si>
+    <t>9.3p</t>
+  </si>
+  <si>
+    <t>0.75u</t>
+  </si>
+  <si>
+    <t>9.25u</t>
+  </si>
+  <si>
+    <t>5.0u</t>
+  </si>
+  <si>
+    <t>7.0u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959558029682_tt</t>
+  </si>
+  <si>
+    <t>8.7p</t>
+  </si>
+  <si>
+    <t>8.25u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959566443472_tt</t>
+  </si>
+  <si>
+    <t>8.6p</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>tmp_2024110813095985417622_tt</t>
+  </si>
+  <si>
+    <t>8.0p</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959573154590_tt</t>
+  </si>
+  <si>
+    <t>9.2p</t>
+  </si>
+  <si>
+    <t>3.25u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959579293021_tt</t>
+  </si>
+  <si>
+    <t>6.5u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959577394818_tt</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959557797891_tt</t>
+  </si>
+  <si>
+    <t>7.2p</t>
+  </si>
+  <si>
+    <t>6.75u</t>
+  </si>
+  <si>
+    <t>tmp_20241108130959557668491_tt</t>
+  </si>
+  <si>
+    <t>tmp_20241108131000557785591_tt</t>
+  </si>
+  <si>
+    <t>tmp_20241108131000585858949_tt</t>
+  </si>
+  <si>
+    <t>5.9p</t>
   </si>
 </sst>
 </file>
@@ -853,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C9FDA6-E018-BB45-9E12-FF2210F3FEFA}">
-  <dimension ref="A1:CP4"/>
+  <dimension ref="A1:CP17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:94" s="2" customFormat="1">
@@ -1142,854 +1271,4546 @@
     </row>
     <row r="2" spans="1:94" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2">
+        <v>-0.17095224540654089</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1.18954E-5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1.131111111111071E-3</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1.1555555555554781E-3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1.464646464647088E-3</v>
+      </c>
+      <c r="H2" s="2">
+        <v>58.874879743396782</v>
+      </c>
+      <c r="I2" s="2">
+        <v>56.593752140529297</v>
+      </c>
+      <c r="J2" s="2">
+        <v>41.169289204272602</v>
+      </c>
+      <c r="K2" s="2">
+        <v>20.15419314301089</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1.7456779737936241</v>
+      </c>
+      <c r="M2" s="2">
+        <v>57.801359794172257</v>
+      </c>
+      <c r="N2" s="2">
+        <v>55.944724914989848</v>
+      </c>
+      <c r="O2" s="2">
+        <v>41.196454012723578</v>
+      </c>
+      <c r="P2" s="2">
+        <v>20.165217935811299</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2.2523659698260898</v>
+      </c>
+      <c r="R2" s="2">
+        <v>61.80592</v>
+      </c>
+      <c r="S2" s="2">
+        <v>518395.5</v>
+      </c>
+      <c r="T2" s="2">
+        <v>67.77373</v>
+      </c>
+      <c r="U2" s="2">
+        <v>522113.3</v>
+      </c>
+      <c r="V2" s="2">
+        <v>64.97645</v>
+      </c>
+      <c r="W2" s="2">
+        <v>459112</v>
+      </c>
+      <c r="X2" s="2">
+        <v>67.580280000000002</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>537937.1</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0.101685</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>7.2303999999999979E-2</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>7.6585000000000014E-2</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>6.4118999999999982E-2</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="2">
-        <v>14.106633521377899</v>
-      </c>
-      <c r="D2" s="2">
-        <v>7.9872000000000004E-6</v>
-      </c>
-      <c r="E2" s="2">
-        <v>8.6666666666691673E-5</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1.333333333334667E-4</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1.9898989898978958E-3</v>
-      </c>
-      <c r="H2" s="2">
-        <v>84.365331294793492</v>
-      </c>
-      <c r="I2" s="2">
-        <v>69.548347014144895</v>
-      </c>
-      <c r="J2" s="2">
-        <v>50.445033433284252</v>
-      </c>
-      <c r="K2" s="2">
-        <v>29.289671113255249</v>
-      </c>
-      <c r="L2" s="2">
-        <v>11.33608804264027</v>
-      </c>
-      <c r="M2" s="2">
-        <v>88.45341151727402</v>
-      </c>
-      <c r="N2" s="2">
-        <v>69.717645937420457</v>
-      </c>
-      <c r="O2" s="2">
-        <v>50.528098120533443</v>
-      </c>
-      <c r="P2" s="2">
-        <v>29.36045086964749</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>11.419250146723099</v>
-      </c>
-      <c r="R2" s="2">
-        <v>88.966719999999995</v>
-      </c>
-      <c r="S2" s="2">
-        <v>1854995</v>
-      </c>
-      <c r="T2" s="2">
-        <v>87.659260000000003</v>
-      </c>
-      <c r="U2" s="2">
-        <v>2087974</v>
-      </c>
-      <c r="V2" s="2">
-        <v>89.78013</v>
-      </c>
-      <c r="W2" s="2">
-        <v>1771443</v>
-      </c>
-      <c r="X2" s="2">
-        <v>85.784559999999999</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>2149247</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>9.136500000000003E-2</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>6.9754000000000038E-2</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>7.1340999999999988E-2</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>6.1796000000000018E-2</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="AF2" s="2" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="AG2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AH2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="AL2" s="2" t="s">
         <v>103</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="2" t="s">
         <v>104</v>
       </c>
       <c r="AO2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="BP2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AR2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AS2" s="2" t="s">
+      <c r="CC2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CD2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CE2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CG2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CI2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CJ2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AT2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BV2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="CK2" s="2" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:94" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-0.22416920815501251</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.29237E-5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5.5333333333320829E-4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5.4222222222202439E-4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.2828282828281641E-3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>65.946871918306442</v>
+      </c>
+      <c r="I3" s="2">
+        <v>59.83280040405468</v>
+      </c>
+      <c r="J3" s="2">
+        <v>41.795216017644258</v>
+      </c>
+      <c r="K3" s="2">
+        <v>20.776905670548299</v>
+      </c>
+      <c r="L3" s="2">
+        <v>4.7287616164424797</v>
+      </c>
+      <c r="M3" s="2">
+        <v>64.761046361598574</v>
+      </c>
+      <c r="N3" s="2">
+        <v>59.552049076549459</v>
+      </c>
+      <c r="O3" s="2">
+        <v>41.846965476747528</v>
+      </c>
+      <c r="P3" s="2">
+        <v>20.80486317876386</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5.0329523835398193</v>
+      </c>
+      <c r="R3" s="2">
+        <v>82.031890000000004</v>
+      </c>
+      <c r="S3" s="2">
+        <v>619484.19999999995</v>
+      </c>
+      <c r="T3" s="2">
+        <v>83.177229999999994</v>
+      </c>
+      <c r="U3" s="2">
+        <v>679333.7</v>
+      </c>
+      <c r="V3" s="2">
+        <v>82.601420000000005</v>
+      </c>
+      <c r="W3" s="2">
+        <v>611725.19999999995</v>
+      </c>
+      <c r="X3" s="2">
+        <v>82.871989999999997</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>705518.2</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.100288</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>7.7352000000000032E-2</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>7.9166999999999987E-2</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>6.9045999999999941E-2</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="2">
-        <v>-3.8559915473051001E-3</v>
-      </c>
-      <c r="D3" s="2">
-        <v>8.0703400000000007E-6</v>
-      </c>
-      <c r="E3" s="2">
-        <v>3.1444444444445668E-3</v>
-      </c>
-      <c r="F3" s="2">
-        <v>3.157777777777791E-3</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1.9292929292928961E-3</v>
-      </c>
-      <c r="H3" s="2">
-        <v>49.885014644466338</v>
-      </c>
-      <c r="I3" s="2">
-        <v>49.844125296723007</v>
-      </c>
-      <c r="J3" s="2">
-        <v>47.342550168382651</v>
-      </c>
-      <c r="K3" s="2">
-        <v>29.72347035225426</v>
-      </c>
-      <c r="L3" s="2">
-        <v>11.74811821387982</v>
-      </c>
-      <c r="M3" s="2">
-        <v>49.677912669777967</v>
-      </c>
-      <c r="N3" s="2">
-        <v>49.639556069786053</v>
-      </c>
-      <c r="O3" s="2">
-        <v>47.257720767611247</v>
-      </c>
-      <c r="P3" s="2">
-        <v>29.78376552051505</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>11.82007791383038</v>
-      </c>
-      <c r="R3" s="2">
-        <v>85.845309999999998</v>
-      </c>
-      <c r="S3" s="2">
-        <v>2146060</v>
-      </c>
-      <c r="T3" s="2">
-        <v>88.091210000000004</v>
-      </c>
-      <c r="U3" s="2">
-        <v>2378135</v>
-      </c>
-      <c r="V3" s="2">
-        <v>87.740179999999995</v>
-      </c>
-      <c r="W3" s="2">
-        <v>2082712</v>
-      </c>
-      <c r="X3" s="2">
-        <v>86.935630000000003</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>2451974</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>8.5758999999999974E-2</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>6.7856000000000027E-2</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>6.8945000000000034E-2</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>6.0256000000000032E-2</v>
-      </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AL3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AI3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="AS3" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AU3" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="AV3" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AX3" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AY3" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AZ3" s="2" t="s">
         <v>104</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BB3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="BC3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BJ3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="BF3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BP3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="BL3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BY3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CB3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BS3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA3" s="2" t="s">
+      <c r="CC3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="CB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CD3" s="2" t="s">
+      <c r="CF3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="CE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="CG3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="CH3" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="CI3" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="CJ3" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="CK3" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="CL3" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="CM3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="CN3" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="CO3" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="CP3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:94" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-0.16029624993034641</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.0619600000000001E-5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.9155555555556477E-3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3.864444444444547E-3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.2424242424248031E-3</v>
+      </c>
+      <c r="H4" s="2">
+        <v>48.400300068155538</v>
+      </c>
+      <c r="I4" s="2">
+        <v>48.082042579902527</v>
+      </c>
+      <c r="J4" s="2">
+        <v>39.708944385986612</v>
+      </c>
+      <c r="K4" s="2">
+        <v>19.001853846645648</v>
+      </c>
+      <c r="L4" s="2">
+        <v>6.1786484175301126</v>
+      </c>
+      <c r="M4" s="2">
+        <v>48.062609394223188</v>
+      </c>
+      <c r="N4" s="2">
+        <v>47.770308069733282</v>
+      </c>
+      <c r="O4" s="2">
+        <v>39.699928425242859</v>
+      </c>
+      <c r="P4" s="2">
+        <v>19.017261311020981</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>6.4346110014538844</v>
+      </c>
+      <c r="R4" s="2">
+        <v>76.424869999999999</v>
+      </c>
+      <c r="S4" s="2">
+        <v>1608413</v>
+      </c>
+      <c r="T4" s="2">
+        <v>96.932789999999997</v>
+      </c>
+      <c r="U4" s="2">
+        <v>592489.19999999995</v>
+      </c>
+      <c r="V4" s="2">
+        <v>77.551720000000003</v>
+      </c>
+      <c r="W4" s="2">
+        <v>1602591</v>
+      </c>
+      <c r="X4" s="2">
+        <v>97.754099999999994</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>612113.5</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.10351200000000001</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>6.9881999999999944E-2</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>8.6500999999999939E-2</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>6.6352000000000022E-2</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF4" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="AG4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BY4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BZ4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CB4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="CC4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CD4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CE4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="CF4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CG4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="CI4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CJ4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CK4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CN4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP4" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:94" s="2" customFormat="1">
+      <c r="A5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-0.15156400456140859</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1.0694699999999999E-5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2.475555555555441E-3</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2.495555555555523E-3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1.585858585859331E-3</v>
+      </c>
+      <c r="H5" s="2">
+        <v>52.36404159785905</v>
+      </c>
+      <c r="I5" s="2">
+        <v>51.596790915525688</v>
+      </c>
+      <c r="J5" s="2">
+        <v>40.016174311342283</v>
+      </c>
+      <c r="K5" s="2">
+        <v>19.41412321044993</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2.6570048882719171</v>
+      </c>
+      <c r="M5" s="2">
+        <v>51.874837981159303</v>
+      </c>
+      <c r="N5" s="2">
+        <v>51.191478618801938</v>
+      </c>
+      <c r="O5" s="2">
+        <v>40.037954206663713</v>
+      </c>
+      <c r="P5" s="2">
+        <v>19.436938014531801</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>3.132567145536497</v>
+      </c>
+      <c r="R5" s="2">
+        <v>73.361599999999996</v>
+      </c>
+      <c r="S5" s="2">
+        <v>492334.1</v>
+      </c>
+      <c r="T5" s="2">
+        <v>75.869699999999995</v>
+      </c>
+      <c r="U5" s="2">
+        <v>498052.2</v>
+      </c>
+      <c r="V5" s="2">
+        <v>75.759519999999995</v>
+      </c>
+      <c r="W5" s="2">
+        <v>441516.6</v>
+      </c>
+      <c r="X5" s="2">
+        <v>75.576800000000006</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>517248.3</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>9.8157999999999967E-2</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>7.2975999999999985E-2</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>8.0404000000000031E-2</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>6.7996999999999974E-2</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="2">
-        <v>-4.8083561684613002E-3</v>
-      </c>
-      <c r="D4" s="2">
-        <v>8.0991199999999998E-6</v>
-      </c>
-      <c r="E4" s="2">
-        <v>5.8222222222218778E-4</v>
-      </c>
-      <c r="F4" s="2">
-        <v>6.5111111111108388E-4</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2.6969696969698712E-3</v>
-      </c>
-      <c r="H4" s="2">
-        <v>66.789292786619711</v>
-      </c>
-      <c r="I4" s="2">
-        <v>65.279952056677544</v>
-      </c>
-      <c r="J4" s="2">
-        <v>51.232911148766149</v>
-      </c>
-      <c r="K4" s="2">
-        <v>30.26839973142059</v>
-      </c>
-      <c r="L4" s="2">
-        <v>12.402724392604149</v>
-      </c>
-      <c r="M4" s="2">
-        <v>65.331842924836067</v>
-      </c>
-      <c r="N4" s="2">
-        <v>64.222788556010187</v>
-      </c>
-      <c r="O4" s="2">
-        <v>51.272170175603407</v>
-      </c>
-      <c r="P4" s="2">
-        <v>30.34744866543496</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>12.482537912788381</v>
-      </c>
-      <c r="R4" s="2">
-        <v>92.859960000000001</v>
-      </c>
-      <c r="S4" s="2">
-        <v>2232089</v>
-      </c>
-      <c r="T4" s="2">
-        <v>92.156769999999995</v>
-      </c>
-      <c r="U4" s="2">
-        <v>2485515</v>
-      </c>
-      <c r="V4" s="2">
-        <v>93.997230000000002</v>
-      </c>
-      <c r="W4" s="2">
-        <v>2061732</v>
-      </c>
-      <c r="X4" s="2">
-        <v>90.980689999999996</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>2523386</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>9.1458000000000039E-2</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>6.6691999999999974E-2</v>
-      </c>
-      <c r="AB4" s="2">
-        <v>7.179000000000002E-2</v>
-      </c>
-      <c r="AC4" s="2">
-        <v>5.8847000000000038E-2</v>
-      </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AF5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CC5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CD5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CF5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CJ5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CK5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CN5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP5" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:94" s="2" customFormat="1">
+      <c r="A6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-0.2399480505318691</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1.39422E-5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.228888888888959E-3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2.2155555555554889E-3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1.454545454545788E-3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>53.213017525947834</v>
+      </c>
+      <c r="I6" s="2">
+        <v>52.604244963861802</v>
+      </c>
+      <c r="J6" s="2">
+        <v>41.859384449855987</v>
+      </c>
+      <c r="K6" s="2">
+        <v>20.871675989339209</v>
+      </c>
+      <c r="L6" s="2">
+        <v>5.6471866116412164</v>
+      </c>
+      <c r="M6" s="2">
+        <v>52.852594364931257</v>
+      </c>
+      <c r="N6" s="2">
+        <v>52.296477712594573</v>
+      </c>
+      <c r="O6" s="2">
+        <v>41.886422724061617</v>
+      </c>
+      <c r="P6" s="2">
+        <v>20.90999167102785</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>5.8668323399986742</v>
+      </c>
+      <c r="R6" s="2">
+        <v>89.819720000000004</v>
+      </c>
+      <c r="S6" s="2">
+        <v>711475.6</v>
+      </c>
+      <c r="T6" s="2">
+        <v>90.106960000000001</v>
+      </c>
+      <c r="U6" s="2">
+        <v>772577.4</v>
+      </c>
+      <c r="V6" s="2">
+        <v>90.310940000000002</v>
+      </c>
+      <c r="W6" s="2">
+        <v>683074.4</v>
+      </c>
+      <c r="X6" s="2">
+        <v>90.167259999999999</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>790862.8</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0.1034869999999999</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>6.7749000000000004E-2</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>8.3337999999999912E-2</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>6.2724000000000002E-2</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BU6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BY6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BZ6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CC6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CD6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CF6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CJ6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CK6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CL6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CO6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP6" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:94" s="2" customFormat="1">
+      <c r="A7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.22774598884332059</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1.26217E-5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.866666666666697E-3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2.855555555555759E-3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1.7070707070704521E-3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>51.273115417849063</v>
+      </c>
+      <c r="I7" s="2">
+        <v>50.787885276039823</v>
+      </c>
+      <c r="J7" s="2">
+        <v>40.889737365786289</v>
+      </c>
+      <c r="K7" s="2">
+        <v>20.146054656906109</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1.9811426417189111</v>
+      </c>
+      <c r="M7" s="2">
+        <v>50.721112987887061</v>
+      </c>
+      <c r="N7" s="2">
+        <v>50.294613784428613</v>
+      </c>
+      <c r="O7" s="2">
+        <v>40.869293437279481</v>
+      </c>
+      <c r="P7" s="2">
+        <v>20.148132850164881</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>2.451636536618508</v>
+      </c>
+      <c r="R7" s="2">
+        <v>66.908950000000004</v>
+      </c>
+      <c r="S7" s="2">
+        <v>556343.1</v>
+      </c>
+      <c r="T7" s="2">
+        <v>69.987930000000006</v>
+      </c>
+      <c r="U7" s="2">
+        <v>560474.5</v>
+      </c>
+      <c r="V7" s="2">
+        <v>69.690280000000001</v>
+      </c>
+      <c r="W7" s="2">
+        <v>498982.1</v>
+      </c>
+      <c r="X7" s="2">
+        <v>69.710070000000002</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>581871.1</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.106507</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>7.3259999999999936E-2</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>8.6758000000000002E-2</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>6.807599999999997E-2</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BN7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BO7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BQ7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BT7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BW7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CC7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CD7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CF7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CG7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CI7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CJ7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CK7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CL7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="CN7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CO7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP7" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:94" s="2" customFormat="1">
+      <c r="A8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.2388537776338279</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.3925400000000001E-5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.4088888888886941E-3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.4000000000000429E-3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1.1717171717172219E-3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>57.365526991929677</v>
+      </c>
+      <c r="I8" s="2">
+        <v>56.135735034964938</v>
+      </c>
+      <c r="J8" s="2">
+        <v>42.821520484372272</v>
+      </c>
+      <c r="K8" s="2">
+        <v>21.90077729555113</v>
+      </c>
+      <c r="L8" s="2">
+        <v>3.843725736303913</v>
+      </c>
+      <c r="M8" s="2">
+        <v>56.903237725960267</v>
+      </c>
+      <c r="N8" s="2">
+        <v>55.796606156590741</v>
+      </c>
+      <c r="O8" s="2">
+        <v>42.861703295027887</v>
+      </c>
+      <c r="P8" s="2">
+        <v>21.936953038375162</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>4.091278304071885</v>
+      </c>
+      <c r="R8" s="2">
+        <v>72.942930000000004</v>
+      </c>
+      <c r="S8" s="2">
+        <v>715126.1</v>
+      </c>
+      <c r="T8" s="2">
+        <v>74.760429999999999</v>
+      </c>
+      <c r="U8" s="2">
+        <v>768911.3</v>
+      </c>
+      <c r="V8" s="2">
+        <v>73.743319999999997</v>
+      </c>
+      <c r="W8" s="2">
+        <v>696839.7</v>
+      </c>
+      <c r="X8" s="2">
+        <v>74.342709999999997</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>787136</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.10347000000000001</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>7.4575999999999976E-2</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>7.9075000000000006E-2</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>6.537300000000007E-2</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="BB8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="BE8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BO8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BP8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BQ8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BR8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BU8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BY8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BZ8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CB8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CC8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CD8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CF8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CI8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CJ8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CK8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CL8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CN8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP8" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:94" s="2" customFormat="1">
+      <c r="A9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="2">
+        <v>-0.25355757860885408</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1.28559E-5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.2822222222222358E-3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3.197777777777831E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1.6565656565656311E-3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>49.685355305694102</v>
+      </c>
+      <c r="I9" s="2">
+        <v>49.324556395848909</v>
+      </c>
+      <c r="J9" s="2">
+        <v>40.499370816527019</v>
+      </c>
+      <c r="K9" s="2">
+        <v>19.533907902772061</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2.151691401814992</v>
+      </c>
+      <c r="M9" s="2">
+        <v>49.299387590134032</v>
+      </c>
+      <c r="N9" s="2">
+        <v>48.9711035135728</v>
+      </c>
+      <c r="O9" s="2">
+        <v>40.486006712619762</v>
+      </c>
+      <c r="P9" s="2">
+        <v>19.539605922806299</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>2.5620877409004361</v>
+      </c>
+      <c r="R9" s="2">
+        <v>67.003469999999993</v>
+      </c>
+      <c r="S9" s="2">
+        <v>547592.80000000005</v>
+      </c>
+      <c r="T9" s="2">
+        <v>69.545109999999994</v>
+      </c>
+      <c r="U9" s="2">
+        <v>554108.6</v>
+      </c>
+      <c r="V9" s="2">
+        <v>67.899640000000005</v>
+      </c>
+      <c r="W9" s="2">
+        <v>547866</v>
+      </c>
+      <c r="X9" s="2">
+        <v>69.739940000000004</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>573650.4</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.110849</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>7.6249999999999984E-2</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>9.130499999999997E-2</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>7.0602999999999971E-2</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AX9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BD9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BG9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BN9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BO9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BQ9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BR9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BY9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BZ9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CD9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CF9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CJ9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CK9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CN9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP9" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:94" s="2" customFormat="1">
+      <c r="A10" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-0.16975206141843899</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.2443600000000001E-5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2.1200000000000229E-3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2.1422222222223911E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1.808080808081214E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>53.534661923264487</v>
+      </c>
+      <c r="I10" s="2">
+        <v>52.762798394569501</v>
+      </c>
+      <c r="J10" s="2">
+        <v>41.140439461264513</v>
+      </c>
+      <c r="K10" s="2">
+        <v>20.205451633066321</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4.7746916099265944</v>
+      </c>
+      <c r="M10" s="2">
+        <v>53.131572316443602</v>
+      </c>
+      <c r="N10" s="2">
+        <v>52.434853864777168</v>
+      </c>
+      <c r="O10" s="2">
+        <v>41.191183799825147</v>
+      </c>
+      <c r="P10" s="2">
+        <v>20.26150623246793</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>4.9873590693830341</v>
+      </c>
+      <c r="R10" s="2">
+        <v>85.02758</v>
+      </c>
+      <c r="S10" s="2">
+        <v>592437.69999999995</v>
+      </c>
+      <c r="T10" s="2">
+        <v>86.251099999999994</v>
+      </c>
+      <c r="U10" s="2">
+        <v>627947</v>
+      </c>
+      <c r="V10" s="2">
+        <v>86.105180000000004</v>
+      </c>
+      <c r="W10" s="2">
+        <v>552984</v>
+      </c>
+      <c r="X10" s="2">
+        <v>86.589410000000001</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>637900</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>7.724999999999993E-2</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>5.846399999999996E-2</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>5.8723999999999998E-2</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>5.2699999999999969E-2</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BB10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BE10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BJ10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BO10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BR10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BT10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BU10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BY10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BZ10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CB10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CD10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CE10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CG10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CI10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CJ10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CK10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CN10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP10" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:94" s="2" customFormat="1">
+      <c r="A11" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-0.2069262291669404</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.33657E-5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1.246666666666742E-3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.1799999999998849E-3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1.515151515151348E-3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>58.56226159236175</v>
+      </c>
+      <c r="I11" s="2">
+        <v>56.727831368171032</v>
+      </c>
+      <c r="J11" s="2">
+        <v>42.05231384963443</v>
+      </c>
+      <c r="K11" s="2">
+        <v>21.62342489795633</v>
+      </c>
+      <c r="L11" s="2">
+        <v>4.104688785913889</v>
+      </c>
+      <c r="M11" s="2">
+        <v>57.586719180384868</v>
+      </c>
+      <c r="N11" s="2">
+        <v>56.081409082951453</v>
+      </c>
+      <c r="O11" s="2">
+        <v>42.083267885347418</v>
+      </c>
+      <c r="P11" s="2">
+        <v>21.65578546890891</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>4.3796573435870636</v>
+      </c>
+      <c r="R11" s="2">
+        <v>77.065759999999997</v>
+      </c>
+      <c r="S11" s="2">
+        <v>672854.9</v>
+      </c>
+      <c r="T11" s="2">
+        <v>79.514259999999993</v>
+      </c>
+      <c r="U11" s="2">
+        <v>729589.1</v>
+      </c>
+      <c r="V11" s="2">
+        <v>77.717479999999995</v>
+      </c>
+      <c r="W11" s="2">
+        <v>660317.5</v>
+      </c>
+      <c r="X11" s="2">
+        <v>79.094239999999999</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>750339.8</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.10248599999999999</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>7.3306999999999956E-2</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>7.5563999999999965E-2</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>6.2650000000000039E-2</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BB11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BE11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BQ11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BT11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BW11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BY11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BZ11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CC11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CD11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CE11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CF11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CG11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CI11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CJ11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CK11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CN11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP11" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:94" s="2" customFormat="1">
+      <c r="A12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-0.1738373577477075</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1.13384E-5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.388888888888859E-3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.4177777777778389E-3</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.3232323232322449E-3</v>
+      </c>
+      <c r="H12" s="2">
+        <v>56.894417121406462</v>
+      </c>
+      <c r="I12" s="2">
+        <v>55.414478942207303</v>
+      </c>
+      <c r="J12" s="2">
+        <v>41.460496897854263</v>
+      </c>
+      <c r="K12" s="2">
+        <v>20.90215963436674</v>
+      </c>
+      <c r="L12" s="2">
+        <v>6.0567372491575906</v>
+      </c>
+      <c r="M12" s="2">
+        <v>56.628661421528989</v>
+      </c>
+      <c r="N12" s="2">
+        <v>55.241859298565167</v>
+      </c>
+      <c r="O12" s="2">
+        <v>41.515210191095953</v>
+      </c>
+      <c r="P12" s="2">
+        <v>20.940019483332041</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>6.3300881455354414</v>
+      </c>
+      <c r="R12" s="2">
+        <v>92.641419999999997</v>
+      </c>
+      <c r="S12" s="2">
+        <v>650483.9</v>
+      </c>
+      <c r="T12" s="2">
+        <v>93.952680000000001</v>
+      </c>
+      <c r="U12" s="2">
+        <v>738986.4</v>
+      </c>
+      <c r="V12" s="2">
+        <v>92.935689999999994</v>
+      </c>
+      <c r="W12" s="2">
+        <v>638167</v>
+      </c>
+      <c r="X12" s="2">
+        <v>93.811880000000002</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>757343.5</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.102908</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>8.0120999999999998E-2</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>7.6846999999999999E-2</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>6.7915000000000003E-2</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AZ12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BG12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BQ12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BU12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BW12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BY12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BZ12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CB12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CC12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CD12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CE12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CF12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CG12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CI12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="CK12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="CN12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP12" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:94" s="2" customFormat="1">
+      <c r="A13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="2">
+        <v>-0.2141977632941065</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1.29774E-5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2.6666666666693341E-5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3.777777777787724E-5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.454545454544666E-3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>79.983891099692613</v>
+      </c>
+      <c r="I13" s="2">
+        <v>61.017263212161872</v>
+      </c>
+      <c r="J13" s="2">
+        <v>41.841950951574809</v>
+      </c>
+      <c r="K13" s="2">
+        <v>21.08485519563013</v>
+      </c>
+      <c r="L13" s="2">
+        <v>6.0613340941231204</v>
+      </c>
+      <c r="M13" s="2">
+        <v>79.091283702911198</v>
+      </c>
+      <c r="N13" s="2">
+        <v>61.086771075076882</v>
+      </c>
+      <c r="O13" s="2">
+        <v>41.924253527417648</v>
+      </c>
+      <c r="P13" s="2">
+        <v>21.142131185979171</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>6.3272643461880094</v>
+      </c>
+      <c r="R13" s="2">
+        <v>89.365799999999993</v>
+      </c>
+      <c r="S13" s="2">
+        <v>606620.80000000005</v>
+      </c>
+      <c r="T13" s="2">
+        <v>91.360900000000001</v>
+      </c>
+      <c r="U13" s="2">
+        <v>641710</v>
+      </c>
+      <c r="V13" s="2">
+        <v>89.928529999999995</v>
+      </c>
+      <c r="W13" s="2">
+        <v>579110.5</v>
+      </c>
+      <c r="X13" s="2">
+        <v>91.198620000000005</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>659518.80000000005</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>8.9834999999999998E-2</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>8.0527999999999988E-2</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>6.6654999999999909E-2</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>6.8052000000000001E-2</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AY13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AZ13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BE13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BN13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BO13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BQ13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BR13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BT13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV13" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BW13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BY13" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BZ13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CB13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CC13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="CD13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="CE13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CF13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="CG13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CI13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="CJ13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CK13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CN13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP13" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:94" s="2" customFormat="1">
+      <c r="A14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-0.20368620377006119</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1.32112E-5</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2.7244444444443319E-3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2.7266666666666182E-3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1.4747474747472671E-3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>51.306032909701401</v>
+      </c>
+      <c r="I14" s="2">
+        <v>50.887549887855677</v>
+      </c>
+      <c r="J14" s="2">
+        <v>41.528636823653137</v>
+      </c>
+      <c r="K14" s="2">
+        <v>20.914161851909149</v>
+      </c>
+      <c r="L14" s="2">
+        <v>6.1838029717633489</v>
+      </c>
+      <c r="M14" s="2">
+        <v>51.038795543517303</v>
+      </c>
+      <c r="N14" s="2">
+        <v>50.648340253552703</v>
+      </c>
+      <c r="O14" s="2">
+        <v>41.542084961964328</v>
+      </c>
+      <c r="P14" s="2">
+        <v>20.933458318019611</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>6.4737917698070042</v>
+      </c>
+      <c r="R14" s="2">
+        <v>91.30668</v>
+      </c>
+      <c r="S14" s="2">
+        <v>637486.9</v>
+      </c>
+      <c r="T14" s="2">
+        <v>91.857560000000007</v>
+      </c>
+      <c r="U14" s="2">
+        <v>710412.2</v>
+      </c>
+      <c r="V14" s="2">
+        <v>91.807339999999996</v>
+      </c>
+      <c r="W14" s="2">
+        <v>623784.69999999995</v>
+      </c>
+      <c r="X14" s="2">
+        <v>91.885959999999997</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>738834.9</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>9.1944000000000026E-2</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>7.2921999999999987E-2</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>7.2663000000000033E-2</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>6.508699999999995E-2</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BB14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BD14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BE14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BN14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BQ14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="BT14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BU14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BY14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BZ14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CB14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CC14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CF14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CG14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CI14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CJ14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CK14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CL14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CN14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CO14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP14" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:94" s="2" customFormat="1">
+      <c r="A15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="2">
+        <v>-0.17054538357448021</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1.23257E-5</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2.068888888888923E-3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2.0755555555555341E-3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1.515151515151348E-3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>54.402499063095732</v>
+      </c>
+      <c r="I15" s="2">
+        <v>53.464141498908063</v>
+      </c>
+      <c r="J15" s="2">
+        <v>41.119146338881457</v>
+      </c>
+      <c r="K15" s="2">
+        <v>19.7858639358905</v>
+      </c>
+      <c r="L15" s="2">
+        <v>2.289428637160253</v>
+      </c>
+      <c r="M15" s="2">
+        <v>53.853287835259053</v>
+      </c>
+      <c r="N15" s="2">
+        <v>53.025176311885929</v>
+      </c>
+      <c r="O15" s="2">
+        <v>41.139196172581208</v>
+      </c>
+      <c r="P15" s="2">
+        <v>19.80007981252578</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>2.7325712909919582</v>
+      </c>
+      <c r="R15" s="2">
+        <v>65.440119999999993</v>
+      </c>
+      <c r="S15" s="2">
+        <v>532299.9</v>
+      </c>
+      <c r="T15" s="2">
+        <v>68.862319999999997</v>
+      </c>
+      <c r="U15" s="2">
+        <v>530420.4</v>
+      </c>
+      <c r="V15" s="2">
+        <v>67.483949999999993</v>
+      </c>
+      <c r="W15" s="2">
+        <v>493316.6</v>
+      </c>
+      <c r="X15" s="2">
+        <v>69.197749999999999</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>547879.9</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>8.8486999999999982E-2</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>6.7794999999999994E-2</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>7.1882000000000001E-2</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>6.3296999999999992E-2</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="2" t="s">
+      <c r="AY15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BA15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BG15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BQ15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BR15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BW15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CB15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CC15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CD15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CE15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CF15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CI15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CJ15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CK15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CL15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="CN15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP15" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:94" s="2" customFormat="1">
+      <c r="A16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-0.2240334619520104</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1.4436100000000001E-5</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.1733333333334099E-3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.1577777777779012E-3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2.2525252525249818E-3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>53.481427005119507</v>
+      </c>
+      <c r="I16" s="2">
+        <v>52.782956505531907</v>
+      </c>
+      <c r="J16" s="2">
+        <v>41.529735340785393</v>
+      </c>
+      <c r="K16" s="2">
+        <v>20.52671922322769</v>
+      </c>
+      <c r="L16" s="2">
+        <v>2.7836660093696328</v>
+      </c>
+      <c r="M16" s="2">
+        <v>53.003310134274159</v>
+      </c>
+      <c r="N16" s="2">
+        <v>52.384871942945459</v>
+      </c>
+      <c r="O16" s="2">
+        <v>41.582368926406467</v>
+      </c>
+      <c r="P16" s="2">
+        <v>20.594854679461889</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>2.9906457415923908</v>
+      </c>
+      <c r="R16" s="2">
+        <v>70.231049999999996</v>
+      </c>
+      <c r="S16" s="2">
+        <v>552309.5</v>
+      </c>
+      <c r="T16" s="2">
+        <v>74.114400000000003</v>
+      </c>
+      <c r="U16" s="2">
+        <v>561202.69999999995</v>
+      </c>
+      <c r="V16" s="2">
+        <v>71.627330000000001</v>
+      </c>
+      <c r="W16" s="2">
+        <v>533752.69999999995</v>
+      </c>
+      <c r="X16" s="2">
+        <v>74.67841</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>564109.30000000005</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>7.4394000000000071E-2</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>5.9974000000000027E-2</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>5.721900000000002E-2</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>5.2798999999999978E-2</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG4" s="2" t="s">
+      <c r="AI16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="2" t="s">
+      <c r="AL16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
+      <c r="AS16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BG16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BH16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BP16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BR16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BU16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BW16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BY16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CB16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CD16" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AK4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AM4" s="2" t="s">
+      <c r="CE16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CH16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CI16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CJ16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CK16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CN16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP16" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:94" s="2" customFormat="1">
+      <c r="A17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="2">
+        <v>-0.13799888144025929</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1.1433999999999999E-5</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.593333333333262E-3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.4155555555555529E-3</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.909090909090856E-3</v>
+      </c>
+      <c r="H17" s="2">
+        <v>54.414518857729341</v>
+      </c>
+      <c r="I17" s="2">
+        <v>53.517297098561677</v>
+      </c>
+      <c r="J17" s="2">
+        <v>41.346230142658172</v>
+      </c>
+      <c r="K17" s="2">
+        <v>20.650141159277538</v>
+      </c>
+      <c r="L17" s="2">
+        <v>6.1399034026982582</v>
+      </c>
+      <c r="M17" s="2">
+        <v>54.839130083139807</v>
+      </c>
+      <c r="N17" s="2">
+        <v>53.871898436856831</v>
+      </c>
+      <c r="O17" s="2">
+        <v>41.424850763435231</v>
+      </c>
+      <c r="P17" s="2">
+        <v>20.683383094541359</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>6.3387299764647</v>
+      </c>
+      <c r="R17" s="2">
+        <v>58.70091</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1592095</v>
+      </c>
+      <c r="T17" s="2">
+        <v>97.789140000000003</v>
+      </c>
+      <c r="U17" s="2">
+        <v>748855.9</v>
+      </c>
+      <c r="V17" s="2">
+        <v>55.834000000000003</v>
+      </c>
+      <c r="W17" s="2">
+        <v>1526450</v>
+      </c>
+      <c r="X17" s="2">
+        <v>97.955079999999995</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>768030.6</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>9.0816999999999926E-2</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>6.638000000000005E-2</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>6.5282000000000062E-2</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>5.6263999999999981E-2</v>
+      </c>
+      <c r="AD17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AP17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BA17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BG17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BH17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BL17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AN4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AP4" s="2" t="s">
+      <c r="BP17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BQ17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BR17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BT17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BU17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BW17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BY17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AQ4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS4" s="2" t="s">
+      <c r="CB17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CC17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CD17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AT4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AW4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AY4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BA4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BB4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC4" s="2" t="s">
+      <c r="CE17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CF17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BD4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BF4" s="2" t="s">
+      <c r="CG17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CH17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CI17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BG4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BH4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BJ4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL4" s="2" t="s">
+      <c r="CJ17" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="BM4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BN4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BO4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BQ4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BR4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BS4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BT4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BU4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BV4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BW4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BX4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BY4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BZ4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="CB4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CC4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CD4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CE4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CF4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CG4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="CH4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CI4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CJ4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="CK4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CL4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CM4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="CN4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CO4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CP4" s="2" t="s">
-        <v>105</v>
+      <c r="CK17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CN17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP17" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
